--- a/Data/Changelog/Italian.xlsx
+++ b/Data/Changelog/Italian.xlsx
@@ -71,6 +71,27 @@
   </x:si>
   <x:si>
     <x:t>Changed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026/08/02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Village\Merchant\Discount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>For a fellow adventurer, I'll give you a discount. Don't tell anyone!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Per un compagno avventuriero, ti faccio uno sconto. Non dirlo a nessuno!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Per un compagno, ti faccio uno sconto. Non dirlo a nessuno!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pending</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -421,7 +442,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J2"/>
+  <x:dimension ref="A1:J3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="1.710625" style="0" customWidth="1"/>
@@ -432,11 +453,11 @@
     <x:col min="6" max="6" width="25.996339" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="64.139196" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="91.282054" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20.710625" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="55.282054" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="8.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:10">
+    <x:row r="1" spans="1:10" ht="10" customHeight="1">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -468,7 +489,7 @@
         <x:v>9</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:10">
+    <x:row r="2" spans="1:10" ht="10" customHeight="1">
       <x:c r="A2" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
@@ -498,6 +519,38 @@
       </x:c>
       <x:c r="J2" s="0" t="s">
         <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:10" ht="10" customHeight="1">
+      <x:c r="A3" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
